--- a/test-output-template.xlsx
+++ b/test-output-template.xlsx
@@ -1,21 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="30240" windowHeight="12460"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Jan 26" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Sep 25" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Apr 25" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Balance" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="T4a" state="visible" r:id="rId8"/>
+    <sheet name="Jan 26" sheetId="1" r:id="rId1"/>
+    <sheet name="Sep 25" sheetId="2" r:id="rId2"/>
+    <sheet name="Apr 25" sheetId="3" r:id="rId3"/>
+    <sheet name="Balance" sheetId="4" r:id="rId4"/>
+    <sheet name="T4a" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="63">
   <si>
     <t>单号</t>
   </si>
@@ -150,6 +166,27 @@
   </si>
   <si>
     <t>53 Maple Ave</t>
+  </si>
+  <si>
+    <t>4444 Test Lane</t>
+  </si>
+  <si>
+    <t>材料1</t>
+  </si>
+  <si>
+    <t>材料2</t>
+  </si>
+  <si>
+    <t>材料3</t>
+  </si>
+  <si>
+    <t>2月</t>
+  </si>
+  <si>
+    <t>材料4</t>
+  </si>
+  <si>
+    <t>3月</t>
   </si>
   <si>
     <t>9000 Ash Grove Crescent</t>
@@ -188,25 +225,368 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <family val="2"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -214,24 +594,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -553,16 +1219,16 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M142"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M128"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -597,7 +1263,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:12">
       <c r="C2" t="s">
         <v>11</v>
       </c>
@@ -614,7 +1280,8 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <f>F2*G2</f>
+        <f t="shared" ref="H2:H27" si="0">F2*G2</f>
+        <v>693</v>
       </c>
       <c r="K2">
         <v>6300</v>
@@ -623,7 +1290,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:13">
       <c r="C3" t="s">
         <v>15</v>
       </c>
@@ -640,7 +1307,8 @@
         <v>14</v>
       </c>
       <c r="H3">
-        <f>F3*G3</f>
+        <f t="shared" si="0"/>
+        <v>700</v>
       </c>
       <c r="K3">
         <v>1000</v>
@@ -652,12 +1320,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:13">
       <c r="C4" t="s">
         <v>18</v>
       </c>
       <c r="H4">
-        <f>F4*G4</f>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>8400</v>
@@ -669,7 +1338,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -677,7 +1346,8 @@
         <v>4000</v>
       </c>
       <c r="H5">
-        <f>F5*G5</f>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="K5">
         <v>500</v>
@@ -689,156 +1359,184 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>24</v>
       </c>
       <c r="H6">
-        <f>F6*G6</f>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="H7">
-        <f>F7*G7</f>
-      </c>
-    </row>
-    <row r="8" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="8:8">
       <c r="H8">
-        <f>F8*G8</f>
-      </c>
-    </row>
-    <row r="9" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="8:8">
       <c r="H9">
-        <f>F9*G9</f>
-      </c>
-    </row>
-    <row r="10" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="8:8">
       <c r="H10">
-        <f>F10*G10</f>
-      </c>
-    </row>
-    <row r="11" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="8:8">
       <c r="H11">
-        <f>F11*G11</f>
-      </c>
-    </row>
-    <row r="12" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="8:8">
       <c r="H12">
-        <f>F12*G12</f>
-      </c>
-    </row>
-    <row r="13" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="8:8">
       <c r="H13">
-        <f>F13*G13</f>
-      </c>
-    </row>
-    <row r="14" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="8:8">
       <c r="H14">
-        <f>F14*G14</f>
-      </c>
-    </row>
-    <row r="15" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="8:8">
       <c r="H15">
-        <f>F15*G15</f>
-      </c>
-    </row>
-    <row r="16" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="8:8">
       <c r="H16">
-        <f>F16*G16</f>
-      </c>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="8:8">
       <c r="H17">
-        <f>F17*G17</f>
-      </c>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8">
       <c r="H18">
-        <f>F18*G18</f>
-      </c>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="8:8">
       <c r="H19">
-        <f>F19*G19</f>
-      </c>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="8:8">
       <c r="H20">
-        <f>F20*G20</f>
-      </c>
-    </row>
-    <row r="21" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="8:8">
       <c r="H21">
-        <f>F21*G21</f>
-      </c>
-    </row>
-    <row r="22" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="8:8">
       <c r="H22">
-        <f>F22*G22</f>
-      </c>
-    </row>
-    <row r="23" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="8:8">
       <c r="H23">
-        <f>F23*G23</f>
-      </c>
-    </row>
-    <row r="24" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="8:8">
       <c r="H24">
-        <f>F24*G24</f>
-      </c>
-    </row>
-    <row r="25" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="8:8">
       <c r="H25">
-        <f>F25*G25</f>
-      </c>
-    </row>
-    <row r="26" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="8:8">
       <c r="H26">
-        <f>F26*G26</f>
-      </c>
-    </row>
-    <row r="27" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="8:8">
       <c r="H27">
-        <f>F27*G27</f>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
         <v>26</v>
       </c>
       <c r="B28">
         <f>SUM(H28:K28)</f>
+        <v>17593</v>
       </c>
       <c r="H28">
         <f>SUM(H2:H27)</f>
+        <v>1393</v>
       </c>
       <c r="I28">
         <f>SUM(I2:I27)</f>
+        <v>0</v>
       </c>
       <c r="K28">
         <f>SUM(K2:K27)</f>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>27</v>
       </c>
       <c r="B29">
         <f>SUM(B5:B7)</f>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30">
         <f>(B29-B28)/B29</f>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+        <v>-3.39825</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -873,7 +1571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
         <v>29</v>
       </c>
@@ -893,18 +1591,20 @@
         <v>15</v>
       </c>
       <c r="H37">
-        <f>F37*G37</f>
-      </c>
-    </row>
-    <row r="38" spans="3:8" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H37:H49" si="1">F37*G37</f>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="38" spans="3:8">
       <c r="C38" t="s">
         <v>33</v>
       </c>
       <c r="H38">
-        <f>F38*G38</f>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -912,99 +1612,116 @@
         <v>2000</v>
       </c>
       <c r="H39">
-        <f>F39*G39</f>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
         <v>24</v>
       </c>
       <c r="H40">
-        <f>F40*G40</f>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
         <v>25</v>
       </c>
       <c r="H41">
-        <f>F41*G41</f>
-      </c>
-    </row>
-    <row r="42" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="8:8">
       <c r="H42">
-        <f>F42*G42</f>
-      </c>
-    </row>
-    <row r="43" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="8:8">
       <c r="H43">
-        <f>F43*G43</f>
-      </c>
-    </row>
-    <row r="44" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="8:8">
       <c r="H44">
-        <f>F44*G44</f>
-      </c>
-    </row>
-    <row r="45" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="8:8">
       <c r="H45">
-        <f>F45*G45</f>
-      </c>
-    </row>
-    <row r="46" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="8:8">
       <c r="H46">
-        <f>F46*G46</f>
-      </c>
-    </row>
-    <row r="47" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="8:8">
       <c r="H47">
-        <f>F47*G47</f>
-      </c>
-    </row>
-    <row r="48" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="8:8">
       <c r="H48">
-        <f>F48*G48</f>
-      </c>
-    </row>
-    <row r="49" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="8:8">
       <c r="H49">
-        <f>F49*G49</f>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" t="s">
         <v>26</v>
       </c>
       <c r="B50">
         <f>SUM(H50:K50)</f>
+        <v>450</v>
       </c>
       <c r="H50">
         <f>SUM(H37:H49)</f>
+        <v>450</v>
       </c>
       <c r="I50">
         <f>SUM(I37:I49)</f>
+        <v>0</v>
       </c>
       <c r="K50">
         <f>SUM(K37:K49)</f>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>27</v>
       </c>
       <c r="B51">
         <f>SUM(B39:B41)</f>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>28</v>
       </c>
       <c r="B52">
         <f>(B51-B50)/B51</f>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.775</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" t="s">
         <v>0</v>
       </c>
@@ -1039,7 +1756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:12">
       <c r="C56" t="s">
         <v>34</v>
       </c>
@@ -1056,7 +1773,8 @@
         <v>13</v>
       </c>
       <c r="H56">
-        <f>F56*G56</f>
+        <f t="shared" ref="H56:H62" si="2">F56*G56</f>
+        <v>903.5</v>
       </c>
       <c r="K56">
         <v>92.76</v>
@@ -1065,12 +1783,13 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:13">
       <c r="C57" t="s">
         <v>36</v>
       </c>
       <c r="H57">
-        <f>F57*G57</f>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K57">
         <v>78.62</v>
@@ -1082,7 +1801,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:8">
       <c r="C58" t="s">
         <v>34</v>
       </c>
@@ -1099,10 +1818,11 @@
         <v>14</v>
       </c>
       <c r="H58">
-        <f>F58*G58</f>
-      </c>
-    </row>
-    <row r="59" spans="3:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="59" spans="3:9">
       <c r="C59" t="s">
         <v>34</v>
       </c>
@@ -1119,21 +1839,38 @@
         <v>13</v>
       </c>
       <c r="H59">
-        <f>F59*G59</f>
+        <f t="shared" si="2"/>
+        <v>195</v>
       </c>
       <c r="I59">
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13">
       <c r="A60" t="s">
         <v>21</v>
       </c>
       <c r="B60">
         <v>1500</v>
       </c>
+      <c r="C60" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" t="s">
+        <v>32</v>
+      </c>
+      <c r="F60">
+        <v>25</v>
+      </c>
+      <c r="G60">
+        <v>13</v>
+      </c>
       <c r="H60">
-        <f>F60*G60</f>
+        <f t="shared" si="2"/>
+        <v>325</v>
       </c>
       <c r="K60">
         <v>1260</v>
@@ -1145,15 +1882,31 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13">
       <c r="A61" t="s">
         <v>24</v>
       </c>
       <c r="B61">
         <v>800</v>
       </c>
+      <c r="C61" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61" t="s">
+        <v>32</v>
+      </c>
+      <c r="F61">
+        <v>35</v>
+      </c>
+      <c r="G61">
+        <v>13</v>
+      </c>
       <c r="H61">
-        <f>F61*G61</f>
+        <f t="shared" si="2"/>
+        <v>455</v>
       </c>
       <c r="K61">
         <v>700</v>
@@ -1165,48 +1918,70 @@
         <v>41</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
         <v>25</v>
       </c>
+      <c r="C62" t="s">
+        <v>34</v>
+      </c>
+      <c r="D62" t="s">
+        <v>31</v>
+      </c>
+      <c r="E62" t="s">
+        <v>32</v>
+      </c>
+      <c r="F62">
+        <v>45</v>
+      </c>
+      <c r="G62">
+        <v>13</v>
+      </c>
       <c r="H62">
-        <f>F62*G62</f>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>585</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63" t="s">
         <v>26</v>
       </c>
       <c r="B63">
         <f>SUM(H63:K63)</f>
+        <v>4924.88</v>
       </c>
       <c r="H63">
         <f>SUM(H56:H62)</f>
+        <v>2743.5</v>
       </c>
       <c r="I63">
         <f>SUM(I56:I62)</f>
+        <v>50</v>
       </c>
       <c r="K63">
         <f>SUM(K56:K62)</f>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2131.38</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>27</v>
       </c>
       <c r="B64">
         <f>SUM(B60:B62)</f>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>28</v>
       </c>
       <c r="B65">
         <f>(B64-B63)/B64</f>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+        <v>-1.14125217391304</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" t="s">
         <v>0</v>
       </c>
@@ -1241,7 +2016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8">
       <c r="A71" t="s">
         <v>42</v>
       </c>
@@ -1261,142 +2036,167 @@
         <v>14</v>
       </c>
       <c r="H71">
-        <f>F71*G71</f>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H71:H89" si="3">F71*G71</f>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" t="s">
         <v>21</v>
       </c>
       <c r="H72">
-        <f>F72*G72</f>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" t="s">
         <v>24</v>
       </c>
       <c r="H73">
-        <f>F73*G73</f>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" t="s">
         <v>25</v>
       </c>
       <c r="H74">
-        <f>F74*G74</f>
-      </c>
-    </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="8:8">
       <c r="H75">
-        <f>F75*G75</f>
-      </c>
-    </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="8:8">
       <c r="H76">
-        <f>F76*G76</f>
-      </c>
-    </row>
-    <row r="77" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="8:8">
       <c r="H77">
-        <f>F77*G77</f>
-      </c>
-    </row>
-    <row r="78" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="8:8">
       <c r="H78">
-        <f>F78*G78</f>
-      </c>
-    </row>
-    <row r="79" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="8:8">
       <c r="H79">
-        <f>F79*G79</f>
-      </c>
-    </row>
-    <row r="80" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="8:8">
       <c r="H80">
-        <f>F80*G80</f>
-      </c>
-    </row>
-    <row r="81" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="8:8">
       <c r="H81">
-        <f>F81*G81</f>
-      </c>
-    </row>
-    <row r="82" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="8:8">
       <c r="H82">
-        <f>F82*G82</f>
-      </c>
-    </row>
-    <row r="83" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="8:8">
       <c r="H83">
-        <f>F83*G83</f>
-      </c>
-    </row>
-    <row r="84" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="8:8">
       <c r="H84">
-        <f>F84*G84</f>
-      </c>
-    </row>
-    <row r="85" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="8:8">
       <c r="H85">
-        <f>F85*G85</f>
-      </c>
-    </row>
-    <row r="86" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="8:8">
       <c r="H86">
-        <f>F86*G86</f>
-      </c>
-    </row>
-    <row r="87" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="8:8">
       <c r="H87">
-        <f>F87*G87</f>
-      </c>
-    </row>
-    <row r="88" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="8:8">
       <c r="H88">
-        <f>F88*G88</f>
-      </c>
-    </row>
-    <row r="89" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="8:8">
       <c r="H89">
-        <f>F89*G89</f>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
       <c r="A90" t="s">
         <v>26</v>
       </c>
       <c r="B90">
         <f>SUM(H90:K90)</f>
+        <v>560</v>
       </c>
       <c r="H90">
         <f>SUM(H71:H89)</f>
+        <v>560</v>
       </c>
       <c r="I90">
         <f>SUM(I71:I89)</f>
+        <v>0</v>
       </c>
       <c r="K90">
         <f>SUM(K71:K89)</f>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91" t="s">
         <v>27</v>
       </c>
       <c r="B91">
         <f>SUM(B72:B74)</f>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92" t="s">
         <v>28</v>
       </c>
-      <c r="B92">
+      <c r="B92" t="e">
         <f>(B91-B90)/B91</f>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
       <c r="A95" t="s">
         <v>0</v>
       </c>
@@ -1431,7 +2231,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:8">
       <c r="C96" t="s">
         <v>44</v>
       </c>
@@ -1448,142 +2248,167 @@
         <v>13</v>
       </c>
       <c r="H96">
-        <f>F96*G96</f>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H96:H114" si="4">F96*G96</f>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
       <c r="A97" t="s">
         <v>21</v>
       </c>
       <c r="H97">
-        <f>F97*G97</f>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98" t="s">
         <v>24</v>
       </c>
       <c r="H98">
-        <f>F98*G98</f>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
       <c r="A99" t="s">
         <v>25</v>
       </c>
       <c r="H99">
-        <f>F99*G99</f>
-      </c>
-    </row>
-    <row r="100" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="8:8">
       <c r="H100">
-        <f>F100*G100</f>
-      </c>
-    </row>
-    <row r="101" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="8:8">
       <c r="H101">
-        <f>F101*G101</f>
-      </c>
-    </row>
-    <row r="102" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="8:8">
       <c r="H102">
-        <f>F102*G102</f>
-      </c>
-    </row>
-    <row r="103" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="8:8">
       <c r="H103">
-        <f>F103*G103</f>
-      </c>
-    </row>
-    <row r="104" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="8:8">
       <c r="H104">
-        <f>F104*G104</f>
-      </c>
-    </row>
-    <row r="105" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="8:8">
       <c r="H105">
-        <f>F105*G105</f>
-      </c>
-    </row>
-    <row r="106" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="8:8">
       <c r="H106">
-        <f>F106*G106</f>
-      </c>
-    </row>
-    <row r="107" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="8:8">
       <c r="H107">
-        <f>F107*G107</f>
-      </c>
-    </row>
-    <row r="108" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="8:8">
       <c r="H108">
-        <f>F108*G108</f>
-      </c>
-    </row>
-    <row r="109" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="8:8">
       <c r="H109">
-        <f>F109*G109</f>
-      </c>
-    </row>
-    <row r="110" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="8:8">
       <c r="H110">
-        <f>F110*G110</f>
-      </c>
-    </row>
-    <row r="111" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="8:8">
       <c r="H111">
-        <f>F111*G111</f>
-      </c>
-    </row>
-    <row r="112" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="8:8">
       <c r="H112">
-        <f>F112*G112</f>
-      </c>
-    </row>
-    <row r="113" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="8:8">
       <c r="H113">
-        <f>F113*G113</f>
-      </c>
-    </row>
-    <row r="114" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="8:8">
       <c r="H114">
-        <f>F114*G114</f>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
       <c r="A115" t="s">
         <v>26</v>
       </c>
       <c r="B115">
         <f>SUM(H115:K115)</f>
+        <v>130</v>
       </c>
       <c r="H115">
         <f>SUM(H96:H114)</f>
+        <v>130</v>
       </c>
       <c r="I115">
         <f>SUM(I96:I114)</f>
+        <v>0</v>
       </c>
       <c r="K115">
         <f>SUM(K96:K114)</f>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
       <c r="A116" t="s">
         <v>27</v>
       </c>
       <c r="B116">
         <f>SUM(B97:B99)</f>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
       <c r="A117" t="s">
         <v>28</v>
       </c>
-      <c r="B117">
+      <c r="B117" t="e">
         <f>(B116-B115)/B116</f>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
       <c r="A120" t="s">
         <v>0</v>
       </c>
@@ -1618,158 +2443,170 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:12">
       <c r="C121" t="s">
-        <v>2</v>
+        <v>45</v>
+      </c>
+      <c r="D121" t="s">
+        <v>12</v>
+      </c>
+      <c r="E121" t="s">
+        <v>13</v>
+      </c>
+      <c r="F121">
+        <v>10</v>
+      </c>
+      <c r="G121">
+        <v>14</v>
       </c>
       <c r="H121">
         <f>F121*G121</f>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>21</v>
+        <v>140</v>
+      </c>
+      <c r="K121">
+        <v>100</v>
+      </c>
+      <c r="L121" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="122" spans="3:12">
+      <c r="C122" t="s">
+        <v>45</v>
+      </c>
+      <c r="D122" t="s">
+        <v>20</v>
+      </c>
+      <c r="E122" t="s">
+        <v>32</v>
+      </c>
+      <c r="F122">
+        <v>5</v>
+      </c>
+      <c r="G122">
+        <v>13</v>
       </c>
       <c r="H122">
         <f>F122*G122</f>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="K122">
+        <v>200</v>
+      </c>
+      <c r="L122" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13">
       <c r="A123" t="s">
-        <v>24</v>
+        <v>21</v>
+      </c>
+      <c r="B123">
+        <v>1000</v>
       </c>
       <c r="H123">
         <f>F123*G123</f>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>300</v>
+      </c>
+      <c r="L123" t="s">
+        <v>22</v>
+      </c>
+      <c r="M123" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13">
       <c r="A124" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H124">
         <f>F124*G124</f>
-      </c>
-    </row>
-    <row r="125" spans="8:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>400</v>
+      </c>
+      <c r="L124" t="s">
+        <v>48</v>
+      </c>
+      <c r="M124" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13">
+      <c r="A125" t="s">
+        <v>25</v>
+      </c>
       <c r="H125">
         <f>F125*G125</f>
-      </c>
-    </row>
-    <row r="126" spans="8:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>500</v>
+      </c>
+      <c r="L125" t="s">
+        <v>50</v>
+      </c>
+      <c r="M125" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" t="s">
+        <v>26</v>
+      </c>
+      <c r="B126">
+        <f>SUM(H126:K126)</f>
+        <v>1705</v>
+      </c>
       <c r="H126">
-        <f>F126*G126</f>
-      </c>
-    </row>
-    <row r="127" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H127">
-        <f>F127*G127</f>
-      </c>
-    </row>
-    <row r="128" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H128">
-        <f>F128*G128</f>
-      </c>
-    </row>
-    <row r="129" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H129">
-        <f>F129*G129</f>
-      </c>
-    </row>
-    <row r="130" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H130">
-        <f>F130*G130</f>
-      </c>
-    </row>
-    <row r="131" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H131">
-        <f>F131*G131</f>
-      </c>
-    </row>
-    <row r="132" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H132">
-        <f>F132*G132</f>
-      </c>
-    </row>
-    <row r="133" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H133">
-        <f>F133*G133</f>
-      </c>
-    </row>
-    <row r="134" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H134">
-        <f>F134*G134</f>
-      </c>
-    </row>
-    <row r="135" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H135">
-        <f>F135*G135</f>
-      </c>
-    </row>
-    <row r="136" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H136">
-        <f>F136*G136</f>
-      </c>
-    </row>
-    <row r="137" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H137">
-        <f>F137*G137</f>
-      </c>
-    </row>
-    <row r="138" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H138">
-        <f>F138*G138</f>
-      </c>
-    </row>
-    <row r="139" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H139">
-        <f>F139*G139</f>
-      </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>26</v>
-      </c>
-      <c r="B140">
-        <f>SUM(H140:K140)</f>
-      </c>
-      <c r="H140">
-        <f>SUM(H121:H139)</f>
-      </c>
-      <c r="I140">
-        <f>SUM(I121:I139)</f>
-      </c>
-      <c r="K140">
-        <f>SUM(K121:K139)</f>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+        <f>SUM(H121:H125)</f>
+        <v>205</v>
+      </c>
+      <c r="I126">
+        <f>SUM(I121:I125)</f>
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <f>SUM(K121:K125)</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
         <v>27</v>
       </c>
-      <c r="B141">
-        <f>SUM(B122:B124)</f>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="B127">
+        <f>SUM(B123:B125)</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
         <v>28</v>
       </c>
-      <c r="B142">
-        <f>(B141-B140)/B141</f>
+      <c r="B128">
+        <f>(B127-B126)/B127</f>
+        <v>-0.705</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K53"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1804,12 +2641,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:8">
       <c r="C2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -1821,10 +2658,11 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <f>F2*G2</f>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H2:H25" si="0">F2*G2</f>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1832,159 +2670,188 @@
         <v>3000</v>
       </c>
       <c r="H3">
-        <f>F3*G3</f>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="H4">
-        <f>F4*G4</f>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="H5">
-        <f>F5*G5</f>
-      </c>
-    </row>
-    <row r="6" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8">
       <c r="H6">
-        <f>F6*G6</f>
-      </c>
-    </row>
-    <row r="7" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="8:8">
       <c r="H7">
-        <f>F7*G7</f>
-      </c>
-    </row>
-    <row r="8" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="8:8">
       <c r="H8">
-        <f>F8*G8</f>
-      </c>
-    </row>
-    <row r="9" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="8:8">
       <c r="H9">
-        <f>F9*G9</f>
-      </c>
-    </row>
-    <row r="10" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="8:8">
       <c r="H10">
-        <f>F10*G10</f>
-      </c>
-    </row>
-    <row r="11" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="8:8">
       <c r="H11">
-        <f>F11*G11</f>
-      </c>
-    </row>
-    <row r="12" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="8:8">
       <c r="H12">
-        <f>F12*G12</f>
-      </c>
-    </row>
-    <row r="13" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="8:8">
       <c r="H13">
-        <f>F13*G13</f>
-      </c>
-    </row>
-    <row r="14" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="8:8">
       <c r="H14">
-        <f>F14*G14</f>
-      </c>
-    </row>
-    <row r="15" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="8:8">
       <c r="H15">
-        <f>F15*G15</f>
-      </c>
-    </row>
-    <row r="16" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="8:8">
       <c r="H16">
-        <f>F16*G16</f>
-      </c>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="8:8">
       <c r="H17">
-        <f>F17*G17</f>
-      </c>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8">
       <c r="H18">
-        <f>F18*G18</f>
-      </c>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="8:8">
       <c r="H19">
-        <f>F19*G19</f>
-      </c>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="8:8">
       <c r="H20">
-        <f>F20*G20</f>
-      </c>
-    </row>
-    <row r="21" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="8:8">
       <c r="H21">
-        <f>F21*G21</f>
-      </c>
-    </row>
-    <row r="22" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="8:8">
       <c r="H22">
-        <f>F22*G22</f>
-      </c>
-    </row>
-    <row r="23" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="8:8">
       <c r="H23">
-        <f>F23*G23</f>
-      </c>
-    </row>
-    <row r="24" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="8:8">
       <c r="H24">
-        <f>F24*G24</f>
-      </c>
-    </row>
-    <row r="25" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="8:8">
       <c r="H25">
-        <f>F25*G25</f>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
         <v>26</v>
       </c>
       <c r="B26">
         <f>SUM(H26:K26)</f>
+        <v>420</v>
       </c>
       <c r="H26">
         <f>SUM(H2:H25)</f>
+        <v>420</v>
       </c>
       <c r="I26">
         <f>SUM(I2:I25)</f>
+        <v>0</v>
       </c>
       <c r="K26">
         <f>SUM(K2:K25)</f>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>27</v>
       </c>
       <c r="B27">
         <f>SUM(B3:B5)</f>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28">
         <f>(B27-B26)/B27</f>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -2019,12 +2886,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:8">
       <c r="C37" t="s">
         <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E37" t="s">
         <v>32</v>
@@ -2036,10 +2903,11 @@
         <v>13</v>
       </c>
       <c r="H37">
-        <f>F37*G37</f>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H37:H50" si="1">F37*G37</f>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -2047,120 +2915,141 @@
         <v>1000</v>
       </c>
       <c r="H38">
-        <f>F38*G38</f>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
         <v>24</v>
       </c>
       <c r="H39">
-        <f>F39*G39</f>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
         <v>25</v>
       </c>
       <c r="H40">
-        <f>F40*G40</f>
-      </c>
-    </row>
-    <row r="41" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="8:8">
       <c r="H41">
-        <f>F41*G41</f>
-      </c>
-    </row>
-    <row r="42" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="8:8">
       <c r="H42">
-        <f>F42*G42</f>
-      </c>
-    </row>
-    <row r="43" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="8:8">
       <c r="H43">
-        <f>F43*G43</f>
-      </c>
-    </row>
-    <row r="44" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="8:8">
       <c r="H44">
-        <f>F44*G44</f>
-      </c>
-    </row>
-    <row r="45" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="8:8">
       <c r="H45">
-        <f>F45*G45</f>
-      </c>
-    </row>
-    <row r="46" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="8:8">
       <c r="H46">
-        <f>F46*G46</f>
-      </c>
-    </row>
-    <row r="47" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="8:8">
       <c r="H47">
-        <f>F47*G47</f>
-      </c>
-    </row>
-    <row r="48" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="8:8">
       <c r="H48">
-        <f>F48*G48</f>
-      </c>
-    </row>
-    <row r="49" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="8:8">
       <c r="H49">
-        <f>F49*G49</f>
-      </c>
-    </row>
-    <row r="50" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="8:8">
       <c r="H50">
-        <f>F50*G50</f>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" t="s">
         <v>26</v>
       </c>
       <c r="B51">
         <f>SUM(H51:K51)</f>
+        <v>260</v>
       </c>
       <c r="H51">
         <f>SUM(H37:H50)</f>
+        <v>260</v>
       </c>
       <c r="I51">
         <f>SUM(I37:I50)</f>
+        <v>0</v>
       </c>
       <c r="K51">
         <f>SUM(K37:K50)</f>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>27</v>
       </c>
       <c r="B52">
         <f>SUM(B38:B40)</f>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>28</v>
       </c>
       <c r="B53">
         <f>(B52-B51)/B52</f>
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2195,12 +3084,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:8">
       <c r="C2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -2212,219 +3101,254 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <f>F2*G2</f>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H2:H25" si="0">F2*G2</f>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>21</v>
       </c>
       <c r="H3">
-        <f>F3*G3</f>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>24</v>
       </c>
       <c r="H4">
-        <f>F4*G4</f>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="H5">
-        <f>F5*G5</f>
-      </c>
-    </row>
-    <row r="6" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="8:8">
       <c r="H6">
-        <f>F6*G6</f>
-      </c>
-    </row>
-    <row r="7" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="8:8">
       <c r="H7">
-        <f>F7*G7</f>
-      </c>
-    </row>
-    <row r="8" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="8:8">
       <c r="H8">
-        <f>F8*G8</f>
-      </c>
-    </row>
-    <row r="9" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="8:8">
       <c r="H9">
-        <f>F9*G9</f>
-      </c>
-    </row>
-    <row r="10" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="8:8">
       <c r="H10">
-        <f>F10*G10</f>
-      </c>
-    </row>
-    <row r="11" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="8:8">
       <c r="H11">
-        <f>F11*G11</f>
-      </c>
-    </row>
-    <row r="12" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="8:8">
       <c r="H12">
-        <f>F12*G12</f>
-      </c>
-    </row>
-    <row r="13" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="8:8">
       <c r="H13">
-        <f>F13*G13</f>
-      </c>
-    </row>
-    <row r="14" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="8:8">
       <c r="H14">
-        <f>F14*G14</f>
-      </c>
-    </row>
-    <row r="15" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="8:8">
       <c r="H15">
-        <f>F15*G15</f>
-      </c>
-    </row>
-    <row r="16" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="8:8">
       <c r="H16">
-        <f>F16*G16</f>
-      </c>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="8:8">
       <c r="H17">
-        <f>F17*G17</f>
-      </c>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8">
       <c r="H18">
-        <f>F18*G18</f>
-      </c>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="8:8">
       <c r="H19">
-        <f>F19*G19</f>
-      </c>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="8:8">
       <c r="H20">
-        <f>F20*G20</f>
-      </c>
-    </row>
-    <row r="21" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="8:8">
       <c r="H21">
-        <f>F21*G21</f>
-      </c>
-    </row>
-    <row r="22" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="8:8">
       <c r="H22">
-        <f>F22*G22</f>
-      </c>
-    </row>
-    <row r="23" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="8:8">
       <c r="H23">
-        <f>F23*G23</f>
-      </c>
-    </row>
-    <row r="24" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="8:8">
       <c r="H24">
-        <f>F24*G24</f>
-      </c>
-    </row>
-    <row r="25" spans="8:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="8:8">
       <c r="H25">
-        <f>F25*G25</f>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
         <v>26</v>
       </c>
       <c r="B26">
         <f>SUM(H26:K26)</f>
+        <v>350</v>
       </c>
       <c r="H26">
         <f>SUM(H2:H25)</f>
+        <v>350</v>
       </c>
       <c r="I26">
         <f>SUM(I2:I25)</f>
+        <v>0</v>
       </c>
       <c r="K26">
         <f>SUM(K2:K25)</f>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>27</v>
       </c>
       <c r="B27">
         <f>SUM(B3:B5)</f>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="e">
         <f>(B27-B26)/B27</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>